--- a/public/excel/product/Giá thép H.xlsx
+++ b/public/excel/product/Giá thép H.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
   <si>
     <t xml:space="preserve">Tên</t>
   </si>
@@ -51,6 +51,9 @@
     <t xml:space="preserve">Loại</t>
   </si>
   <si>
+    <t xml:space="preserve">Lô hàng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thép hình H 100 x 100 x 6 x 8 x 12m</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thép hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM221</t>
   </si>
   <si>
     <t xml:space="preserve">Thép hình H 125 x 125 x 6.5 x 9 x 12m</t>
@@ -372,7 +378,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.28"/>
@@ -409,10 +415,13 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>12</v>
@@ -424,24 +433,27 @@
         <v>19.091</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>12</v>
@@ -453,24 +465,27 @@
         <v>19.091</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>12</v>
@@ -482,24 +497,27 @@
         <v>19.091</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>12</v>
@@ -511,24 +529,27 @@
         <v>19.091</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>12</v>
@@ -540,24 +561,27 @@
         <v>19.091</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>12</v>
@@ -569,24 +593,27 @@
         <v>19.091</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>12</v>
@@ -598,24 +625,27 @@
         <v>19.091</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>12</v>
@@ -627,24 +657,27 @@
         <v>19.091</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>12</v>
@@ -656,24 +689,27 @@
         <v>19.091</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>12</v>
@@ -685,24 +721,27 @@
         <v>19.091</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>12</v>
@@ -714,19 +753,22 @@
         <v>19.091</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
